--- a/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -22,10 +22,6 @@
     <t>int</t>
   </si>
   <si>
-    <t>技能行为类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Type</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -51,6 +47,30 @@
   </si>
   <si>
     <t>Desc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff覆盖方式</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConverType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duration</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时长(毫秒)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -423,49 +443,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:F14"/>
+  <dimension ref="C2:H14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="6" width="12.625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="15.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="F2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -473,53 +507,81 @@
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>5500001</v>
       </c>
-    </row>
-    <row r="7" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C7" s="1">
         <v>5500002</v>
       </c>
-    </row>
-    <row r="8" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="1">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -71,6 +71,14 @@
   </si>
   <si>
     <t>时长(毫秒)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff通知客户端方式</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoticeClientType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -78,7 +86,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,6 +116,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFD0D0D0"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -135,13 +150,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -443,23 +461,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:H14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <dimension ref="C1:K14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="15.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="6" max="8" width="15.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="H2" s="2" t="s">
+    <row r="1" spans="3:11">
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="3:11">
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:11">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -473,13 +494,16 @@
         <v>10</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:11">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -493,13 +517,16 @@
         <v>11</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:11">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -516,10 +543,13 @@
         <v>12</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:11" s="1" customFormat="1">
       <c r="C6" s="1">
         <v>5500001</v>
       </c>
@@ -527,10 +557,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>3000</v>
       </c>
     </row>
-    <row r="7" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:11" s="1" customFormat="1">
       <c r="C7" s="1">
         <v>5500002</v>
       </c>
@@ -538,54 +571,62 @@
         <v>3</v>
       </c>
       <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>3000</v>
       </c>
     </row>
-    <row r="8" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:11" s="1" customFormat="1"/>
+    <row r="9" spans="3:11" s="1" customFormat="1"/>
+    <row r="10" spans="3:11">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="3:11">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="3:11">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="3:11">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="3:11">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -66,19 +66,67 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Duration</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>时长(毫秒)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Buff通知客户端方式</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>NoticeClientType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>层数最大限制</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LayerLimit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始增加层数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FirstAddLayer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>总时长(毫秒)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tick间隔时间(毫秒)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TickTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TickAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RemoveAction</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -461,26 +509,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:K14"/>
+  <dimension ref="C1:Q14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
-    <col min="6" max="8" width="15.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="6" max="14" width="15.625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.625" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11">
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" spans="3:11">
-      <c r="I2" s="2" t="s">
+    <row r="1" spans="3:17">
+      <c r="Q1" s="4"/>
+    </row>
+    <row r="2" spans="3:17">
+      <c r="O2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="3:11">
+    <row r="3" spans="3:17">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -494,16 +542,34 @@
         <v>10</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="3:11">
+    <row r="4" spans="3:17">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -517,16 +583,34 @@
         <v>11</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="3:11">
+    <row r="5" spans="3:17">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -546,10 +630,28 @@
         <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:11" s="1" customFormat="1">
+    <row r="6" spans="3:17" s="1" customFormat="1">
       <c r="C6" s="1">
         <v>5500001</v>
       </c>
@@ -560,10 +662,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
         <v>3000</v>
       </c>
     </row>
-    <row r="7" spans="3:11" s="1" customFormat="1">
+    <row r="7" spans="3:17" s="1" customFormat="1">
       <c r="C7" s="1">
         <v>5500002</v>
       </c>
@@ -574,12 +682,18 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
         <v>3000</v>
       </c>
     </row>
-    <row r="8" spans="3:11" s="1" customFormat="1"/>
-    <row r="9" spans="3:11" s="1" customFormat="1"/>
-    <row r="10" spans="3:11">
+    <row r="8" spans="3:17" s="1" customFormat="1"/>
+    <row r="9" spans="3:17" s="1" customFormat="1"/>
+    <row r="10" spans="3:17">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -587,8 +701,14 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="3:11">
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="3:17">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -596,8 +716,14 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="3:11">
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="3:17">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -605,8 +731,14 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="3:11">
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="3:17">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -614,8 +746,14 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="3:11">
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="3:17">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -623,6 +761,12 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -127,6 +127,10 @@
   </si>
   <si>
     <t>RemoveAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续掉血</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -653,13 +657,16 @@
     </row>
     <row r="6" spans="3:17" s="1" customFormat="1">
       <c r="C6" s="1">
-        <v>5500001</v>
+        <v>55001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -670,10 +677,19 @@
       <c r="J6" s="1">
         <v>3000</v>
       </c>
+      <c r="L6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1">
+        <v>77003</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="7" spans="3:17" s="1" customFormat="1">
       <c r="C7" s="1">
-        <v>5500002</v>
+        <v>55002</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C5188E-0380-4062-AEFB-F055E9D4932C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13065"/>
+    <workbookView xWindow="0" yWindow="4215" windowWidth="26625" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuffProto" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>Id</t>
   </si>
@@ -131,13 +137,21 @@
   </si>
   <si>
     <t>持续掉血</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff自身特效</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OwnerEffect</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -222,14 +236,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -267,7 +284,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -339,7 +356,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -512,27 +529,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:Q14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C1:R14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
-    <col min="6" max="14" width="15.625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.625" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="6" max="15" width="15.625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.625" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17">
-      <c r="Q1" s="4"/>
-    </row>
-    <row r="2" spans="3:17">
-      <c r="O2" s="2" t="s">
+    <row r="1" spans="3:18">
+      <c r="R1" s="4"/>
+    </row>
+    <row r="2" spans="3:18">
+      <c r="P2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="3:17">
+    <row r="3" spans="3:18">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -570,10 +587,13 @@
         <v>21</v>
       </c>
       <c r="O3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="3:17">
+    <row r="4" spans="3:18">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -611,10 +631,13 @@
         <v>28</v>
       </c>
       <c r="O4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="3:17">
+    <row r="5" spans="3:18">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -652,10 +675,13 @@
         <v>23</v>
       </c>
       <c r="O5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:17" s="1" customFormat="1">
+    <row r="6" spans="3:18" s="1" customFormat="1">
       <c r="C6" s="1">
         <v>55001</v>
       </c>
@@ -683,11 +709,11 @@
       <c r="M6" s="1">
         <v>77003</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="3:17" s="1" customFormat="1">
+    <row r="7" spans="3:18" s="1" customFormat="1">
       <c r="C7" s="1">
         <v>55002</v>
       </c>
@@ -707,9 +733,9 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="8" spans="3:17" s="1" customFormat="1"/>
-    <row r="9" spans="3:17" s="1" customFormat="1"/>
-    <row r="10" spans="3:17">
+    <row r="8" spans="3:18" s="1" customFormat="1"/>
+    <row r="9" spans="3:18" s="1" customFormat="1"/>
+    <row r="10" spans="3:18">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -723,8 +749,9 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="3:17">
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="3:18">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -738,8 +765,9 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="3:17">
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="3:18">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -753,8 +781,9 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="3:17">
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="3:18">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -768,8 +797,9 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="3:17">
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="3:18">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -783,6 +813,7 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C5188E-0380-4062-AEFB-F055E9D4932C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216186DE-A8C3-4CA8-BC88-E624B988B027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4215" windowWidth="26625" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2400" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuffProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>Id</t>
   </si>
@@ -145,6 +145,10 @@
   </si>
   <si>
     <t>OwnerEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -545,6 +549,9 @@
       <c r="R1" s="4"/>
     </row>
     <row r="2" spans="3:18">
+      <c r="O2" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="P2" s="2" t="s">
         <v>7</v>
       </c>
@@ -707,7 +714,7 @@
         <v>1000</v>
       </c>
       <c r="M6" s="1">
-        <v>77003</v>
+        <v>77004</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>29</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216186DE-A8C3-4CA8-BC88-E624B988B027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD72CE3-F0E4-4410-88F6-9B86642D7B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2400" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3390" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuffProto" sheetId="1" r:id="rId1"/>
@@ -708,13 +708,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="L6" s="1">
         <v>1000</v>
       </c>
       <c r="M6" s="1">
         <v>77004</v>
+      </c>
+      <c r="O6" s="1">
+        <v>22004</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>29</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD72CE3-F0E4-4410-88F6-9B86642D7B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAC267A-51ED-4ED0-98DD-35C7F20050D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3390" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="825" yWindow="5250" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuffProto" sheetId="1" r:id="rId1"/>
@@ -710,11 +710,17 @@
       <c r="J6" s="1">
         <v>5000</v>
       </c>
+      <c r="K6" s="1">
+        <v>77005</v>
+      </c>
       <c r="L6" s="1">
         <v>1000</v>
       </c>
       <c r="M6" s="1">
         <v>77004</v>
+      </c>
+      <c r="N6" s="1">
+        <v>77005</v>
       </c>
       <c r="O6" s="1">
         <v>22004</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAC267A-51ED-4ED0-98DD-35C7F20050D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A93C885-38C4-4D4C-BE66-BA1AA52BBBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="5250" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuffProto" sheetId="1" r:id="rId1"/>
@@ -708,13 +708,13 @@
         <v>1</v>
       </c>
       <c r="J6" s="1">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="K6" s="1">
         <v>77005</v>
       </c>
       <c r="L6" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M6" s="1">
         <v>77004</v>
